--- a/spectral_centroid/TS9複合音.xlsx
+++ b/spectral_centroid/TS9複合音.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Research\recording_application\spectral_centroid\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E1A3E11-7E49-4346-B367-8EC204C47F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DCB5783-D71F-4943-980D-A80AA9CCFF0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -435,36 +435,6 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:title>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="ja-JP"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -531,61 +501,6 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="ja-JP" altLang="en-US"/>
-                  <a:t>スペクトル重心</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="ja-JP"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -964,7 +879,6 @@
         <c:axId val="1178720208"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="6000"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -2562,15 +2476,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="4" max="4" width="13.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="3"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -2579,7 +2493,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -2599,7 +2513,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -2622,7 +2536,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -2645,7 +2559,7 @@
         <v>1848</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -2668,7 +2582,7 @@
         <v>1927</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -2676,7 +2590,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
@@ -2684,7 +2598,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -2692,7 +2606,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -2700,7 +2614,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
@@ -2708,7 +2622,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -2716,7 +2630,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
@@ -2724,7 +2638,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
@@ -2732,7 +2646,7 @@
         <v>1850</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
@@ -2740,7 +2654,7 @@
         <v>1848</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
@@ -2748,7 +2662,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
@@ -2756,7 +2670,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
@@ -2764,7 +2678,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
@@ -2772,7 +2686,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
@@ -2780,7 +2694,7 @@
         <v>1930</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
@@ -2788,7 +2702,7 @@
         <v>1927</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
